--- a/final_outputs/excel_tables/table_diagnostics.xlsx
+++ b/final_outputs/excel_tables/table_diagnostics.xlsx
@@ -470,7 +470,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00111</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -499,7 +499,7 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00149</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -528,7 +528,7 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0.00129</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -557,7 +557,7 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00139</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -586,7 +586,7 @@
         <v>0.9</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00141</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/final_outputs/excel_tables/table_diagnostics.xlsx
+++ b/final_outputs/excel_tables/table_diagnostics.xlsx
@@ -470,7 +470,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.10134</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -480,7 +480,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -499,7 +499,7 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.06666999999999999</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -528,7 +528,7 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.06438000000000001</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -557,7 +557,7 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.08822000000000001</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -567,7 +567,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -586,7 +586,7 @@
         <v>0.9</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.13065</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -596,7 +596,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
